--- a/Comparison Analysis/Results/Output_monthly_mean_costs-Unadjusted.xlsx
+++ b/Comparison Analysis/Results/Output_monthly_mean_costs-Unadjusted.xlsx
@@ -363,7 +363,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_cost</t>
+          <t>mean_costs</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -387,16 +387,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>102.9305685490057</v>
+        <v>99.05867804288665</v>
       </c>
       <c r="C2">
-        <v>102.931</v>
+        <v>99.059</v>
       </c>
       <c r="D2">
-        <v>101.55</v>
+        <v>97.711</v>
       </c>
       <c r="E2">
-        <v>104.347</v>
+        <v>100.429</v>
       </c>
     </row>
     <row r="3">
@@ -404,16 +404,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>72.04286949873585</v>
+        <v>69.80736881636767</v>
       </c>
       <c r="C3">
-        <v>72.04300000000001</v>
+        <v>69.807</v>
       </c>
       <c r="D3">
-        <v>70.857</v>
+        <v>68.63</v>
       </c>
       <c r="E3">
-        <v>73.15300000000001</v>
+        <v>70.986</v>
       </c>
     </row>
     <row r="4">
@@ -421,16 +421,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>66.31357603678109</v>
+        <v>63.95476160804262</v>
       </c>
       <c r="C4">
-        <v>66.31399999999999</v>
+        <v>63.955</v>
       </c>
       <c r="D4">
-        <v>65.089</v>
+        <v>62.781</v>
       </c>
       <c r="E4">
-        <v>67.56</v>
+        <v>65.087</v>
       </c>
     </row>
     <row r="5">
@@ -438,16 +438,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>54.5070391117053</v>
+        <v>53.12185586057736</v>
       </c>
       <c r="C5">
-        <v>54.507</v>
+        <v>53.122</v>
       </c>
       <c r="D5">
-        <v>53.333</v>
+        <v>52.063</v>
       </c>
       <c r="E5">
-        <v>55.616</v>
+        <v>54.182</v>
       </c>
     </row>
     <row r="6">
@@ -455,16 +455,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50.15316418349769</v>
+        <v>48.50953159837668</v>
       </c>
       <c r="C6">
-        <v>50.153</v>
+        <v>48.51</v>
       </c>
       <c r="D6">
-        <v>49.069</v>
+        <v>47.483</v>
       </c>
       <c r="E6">
-        <v>51.243</v>
+        <v>49.526</v>
       </c>
     </row>
     <row r="7">
@@ -472,16 +472,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>44.99899853109132</v>
+        <v>43.3334185263894</v>
       </c>
       <c r="C7">
-        <v>44.999</v>
+        <v>43.333</v>
       </c>
       <c r="D7">
-        <v>43.942</v>
+        <v>42.414</v>
       </c>
       <c r="E7">
-        <v>46.008</v>
+        <v>44.306</v>
       </c>
     </row>
     <row r="8">
@@ -489,16 +489,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>43.17871147085134</v>
+        <v>41.56185486553372</v>
       </c>
       <c r="C8">
-        <v>43.179</v>
+        <v>41.562</v>
       </c>
       <c r="D8">
-        <v>42.124</v>
+        <v>40.606</v>
       </c>
       <c r="E8">
-        <v>44.18</v>
+        <v>42.529</v>
       </c>
     </row>
     <row r="9">
@@ -506,16 +506,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>39.13646790822757</v>
+        <v>37.7925320473974</v>
       </c>
       <c r="C9">
-        <v>39.136</v>
+        <v>37.793</v>
       </c>
       <c r="D9">
-        <v>38.181</v>
+        <v>36.884</v>
       </c>
       <c r="E9">
-        <v>40.087</v>
+        <v>38.667</v>
       </c>
     </row>
     <row r="10">
@@ -523,16 +523,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.52977404146706</v>
+        <v>37.1954066722423</v>
       </c>
       <c r="C10">
-        <v>38.53</v>
+        <v>37.195</v>
       </c>
       <c r="D10">
-        <v>37.509</v>
+        <v>36.282</v>
       </c>
       <c r="E10">
-        <v>39.564</v>
+        <v>38.114</v>
       </c>
     </row>
     <row r="11">
@@ -540,16 +540,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>36.83765658213668</v>
+        <v>35.62409598657737</v>
       </c>
       <c r="C11">
-        <v>36.838</v>
+        <v>35.624</v>
       </c>
       <c r="D11">
-        <v>35.902</v>
+        <v>34.695</v>
       </c>
       <c r="E11">
-        <v>37.754</v>
+        <v>36.552</v>
       </c>
     </row>
     <row r="12">
@@ -557,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>34.7137153592008</v>
+        <v>33.40428925160928</v>
       </c>
       <c r="C12">
-        <v>34.714</v>
+        <v>33.404</v>
       </c>
       <c r="D12">
-        <v>33.771</v>
+        <v>32.574</v>
       </c>
       <c r="E12">
-        <v>35.638</v>
+        <v>34.228</v>
       </c>
     </row>
     <row r="13">
@@ -574,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35.45677966443888</v>
+        <v>34.21152591672208</v>
       </c>
       <c r="C13">
-        <v>35.457</v>
+        <v>34.212</v>
       </c>
       <c r="D13">
-        <v>34.521</v>
+        <v>33.304</v>
       </c>
       <c r="E13">
-        <v>36.424</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="14">
@@ -591,16 +591,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>32.7982042977835</v>
+        <v>31.57264273751825</v>
       </c>
       <c r="C14">
-        <v>32.798</v>
+        <v>31.573</v>
       </c>
       <c r="D14">
-        <v>31.894</v>
+        <v>30.747</v>
       </c>
       <c r="E14">
-        <v>33.661</v>
+        <v>32.363</v>
       </c>
     </row>
     <row r="15">
@@ -608,16 +608,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>32.36236342144208</v>
+        <v>31.11714387652273</v>
       </c>
       <c r="C15">
-        <v>32.362</v>
+        <v>31.117</v>
       </c>
       <c r="D15">
-        <v>31.445</v>
+        <v>30.259</v>
       </c>
       <c r="E15">
-        <v>33.303</v>
+        <v>31.973</v>
       </c>
     </row>
     <row r="16">
@@ -625,16 +625,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>30.52648522030822</v>
+        <v>29.43357940845804</v>
       </c>
       <c r="C16">
-        <v>30.526</v>
+        <v>29.434</v>
       </c>
       <c r="D16">
-        <v>29.646</v>
+        <v>28.617</v>
       </c>
       <c r="E16">
-        <v>31.377</v>
+        <v>30.227</v>
       </c>
     </row>
     <row r="17">
@@ -642,16 +642,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>29.59164402760683</v>
+        <v>28.57380668938049</v>
       </c>
       <c r="C17">
-        <v>29.592</v>
+        <v>28.574</v>
       </c>
       <c r="D17">
-        <v>28.733</v>
+        <v>27.729</v>
       </c>
       <c r="E17">
-        <v>30.455</v>
+        <v>29.426</v>
       </c>
     </row>
     <row r="18">
@@ -659,16 +659,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28.02754795792075</v>
+        <v>27.05234608666443</v>
       </c>
       <c r="C18">
-        <v>28.028</v>
+        <v>27.052</v>
       </c>
       <c r="D18">
-        <v>27.255</v>
+        <v>26.263</v>
       </c>
       <c r="E18">
-        <v>28.818</v>
+        <v>27.834</v>
       </c>
     </row>
     <row r="19">
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>27.55244949948768</v>
+        <v>26.55599132738752</v>
       </c>
       <c r="C19">
-        <v>27.552</v>
+        <v>26.556</v>
       </c>
       <c r="D19">
-        <v>26.724</v>
+        <v>25.748</v>
       </c>
       <c r="E19">
-        <v>28.417</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="20">
@@ -693,16 +693,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.14468553155065</v>
+        <v>26.15764604519</v>
       </c>
       <c r="C20">
-        <v>27.145</v>
+        <v>26.158</v>
       </c>
       <c r="D20">
-        <v>26.298</v>
+        <v>25.387</v>
       </c>
       <c r="E20">
-        <v>27.996</v>
+        <v>26.924</v>
       </c>
     </row>
     <row r="21">
@@ -710,16 +710,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25.15960007541148</v>
+        <v>24.28707693575919</v>
       </c>
       <c r="C21">
-        <v>25.16</v>
+        <v>24.287</v>
       </c>
       <c r="D21">
-        <v>24.354</v>
+        <v>23.508</v>
       </c>
       <c r="E21">
-        <v>25.969</v>
+        <v>25.028</v>
       </c>
     </row>
     <row r="22">
@@ -727,16 +727,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>25.82929556318664</v>
+        <v>24.89110474111042</v>
       </c>
       <c r="C22">
-        <v>25.829</v>
+        <v>24.891</v>
       </c>
       <c r="D22">
-        <v>24.976</v>
+        <v>24.093</v>
       </c>
       <c r="E22">
-        <v>26.69</v>
+        <v>25.655</v>
       </c>
     </row>
     <row r="23">
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>23.41703385294085</v>
+        <v>22.61530467358593</v>
       </c>
       <c r="C23">
-        <v>23.417</v>
+        <v>22.615</v>
       </c>
       <c r="D23">
-        <v>22.672</v>
+        <v>21.902</v>
       </c>
       <c r="E23">
-        <v>24.174</v>
+        <v>23.339</v>
       </c>
     </row>
     <row r="24">
@@ -761,16 +761,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>23.79645801896145</v>
+        <v>22.94278394151077</v>
       </c>
       <c r="C24">
-        <v>23.796</v>
+        <v>22.943</v>
       </c>
       <c r="D24">
-        <v>22.96</v>
+        <v>22.18</v>
       </c>
       <c r="E24">
-        <v>24.608</v>
+        <v>23.722</v>
       </c>
     </row>
     <row r="25">
@@ -778,16 +778,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>22.04638042408187</v>
+        <v>20.85801345999603</v>
       </c>
       <c r="C25">
-        <v>22.046</v>
+        <v>20.858</v>
       </c>
       <c r="D25">
-        <v>21.311</v>
+        <v>20.119</v>
       </c>
       <c r="E25">
-        <v>22.778</v>
+        <v>21.586</v>
       </c>
     </row>
   </sheetData>
@@ -808,7 +808,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_cost</t>
+          <t>mean_costs</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -832,16 +832,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>107.8430566442464</v>
+        <v>90.82146312041387</v>
       </c>
       <c r="C2">
-        <v>107.843</v>
+        <v>90.821</v>
       </c>
       <c r="D2">
-        <v>106.075</v>
+        <v>89.62</v>
       </c>
       <c r="E2">
-        <v>109.57</v>
+        <v>92.063</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>73.67915704703891</v>
+        <v>63.81400316927204</v>
       </c>
       <c r="C3">
-        <v>73.679</v>
+        <v>63.814</v>
       </c>
       <c r="D3">
-        <v>72.324</v>
+        <v>62.733</v>
       </c>
       <c r="E3">
-        <v>75.075</v>
+        <v>64.883</v>
       </c>
     </row>
     <row r="4">
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>67.98267898191489</v>
+        <v>58.46920665064061</v>
       </c>
       <c r="C4">
-        <v>67.983</v>
+        <v>58.469</v>
       </c>
       <c r="D4">
-        <v>66.517</v>
+        <v>57.413</v>
       </c>
       <c r="E4">
-        <v>69.417</v>
+        <v>59.539</v>
       </c>
     </row>
     <row r="5">
@@ -883,16 +883,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>55.487651019738</v>
+        <v>48.36305309052091</v>
       </c>
       <c r="C5">
-        <v>55.488</v>
+        <v>48.363</v>
       </c>
       <c r="D5">
-        <v>54.241</v>
+        <v>47.443</v>
       </c>
       <c r="E5">
-        <v>56.747</v>
+        <v>49.295</v>
       </c>
     </row>
     <row r="6">
@@ -900,16 +900,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50.19644920966601</v>
+        <v>44.05150886515644</v>
       </c>
       <c r="C6">
-        <v>50.196</v>
+        <v>44.052</v>
       </c>
       <c r="D6">
-        <v>48.913</v>
+        <v>43.11</v>
       </c>
       <c r="E6">
-        <v>51.493</v>
+        <v>44.989</v>
       </c>
     </row>
     <row r="7">
@@ -917,16 +917,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>45.36580870485795</v>
+        <v>39.37389950431164</v>
       </c>
       <c r="C7">
-        <v>45.366</v>
+        <v>39.374</v>
       </c>
       <c r="D7">
-        <v>44.217</v>
+        <v>38.518</v>
       </c>
       <c r="E7">
-        <v>46.539</v>
+        <v>40.252</v>
       </c>
     </row>
     <row r="8">
@@ -934,16 +934,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>43.58758364836262</v>
+        <v>37.81484531259321</v>
       </c>
       <c r="C8">
-        <v>43.588</v>
+        <v>37.815</v>
       </c>
       <c r="D8">
-        <v>42.428</v>
+        <v>36.923</v>
       </c>
       <c r="E8">
-        <v>44.723</v>
+        <v>38.682</v>
       </c>
     </row>
     <row r="9">
@@ -951,16 +951,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>39.37621788766813</v>
+        <v>34.28728516389078</v>
       </c>
       <c r="C9">
-        <v>39.376</v>
+        <v>34.287</v>
       </c>
       <c r="D9">
-        <v>38.299</v>
+        <v>33.431</v>
       </c>
       <c r="E9">
-        <v>40.521</v>
+        <v>35.142</v>
       </c>
     </row>
     <row r="10">
@@ -968,16 +968,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>39.12684050637654</v>
+        <v>33.91752810234615</v>
       </c>
       <c r="C10">
-        <v>39.127</v>
+        <v>33.918</v>
       </c>
       <c r="D10">
-        <v>38.021</v>
+        <v>33.091</v>
       </c>
       <c r="E10">
-        <v>40.232</v>
+        <v>34.763</v>
       </c>
     </row>
     <row r="11">
@@ -985,16 +985,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37.51529230689903</v>
+        <v>32.5645593321123</v>
       </c>
       <c r="C11">
-        <v>37.515</v>
+        <v>32.565</v>
       </c>
       <c r="D11">
-        <v>36.432</v>
+        <v>31.709</v>
       </c>
       <c r="E11">
-        <v>38.584</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="12">
@@ -1002,16 +1002,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>35.09366901384218</v>
+        <v>30.44006724826039</v>
       </c>
       <c r="C12">
-        <v>35.094</v>
+        <v>30.44</v>
       </c>
       <c r="D12">
-        <v>34.034</v>
+        <v>29.604</v>
       </c>
       <c r="E12">
-        <v>36.171</v>
+        <v>31.228</v>
       </c>
     </row>
     <row r="13">
@@ -1019,16 +1019,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35.90562436443723</v>
+        <v>31.27010472960533</v>
       </c>
       <c r="C13">
-        <v>35.906</v>
+        <v>31.27</v>
       </c>
       <c r="D13">
-        <v>34.874</v>
+        <v>30.423</v>
       </c>
       <c r="E13">
-        <v>36.962</v>
+        <v>32.146</v>
       </c>
     </row>
     <row r="14">
@@ -1036,16 +1036,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>33.00314809511802</v>
+        <v>28.73185078501769</v>
       </c>
       <c r="C14">
-        <v>33.003</v>
+        <v>28.732</v>
       </c>
       <c r="D14">
-        <v>32.004</v>
+        <v>27.979</v>
       </c>
       <c r="E14">
-        <v>33.981</v>
+        <v>29.512</v>
       </c>
     </row>
     <row r="15">
@@ -1053,16 +1053,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>32.85118066732093</v>
+        <v>28.3857398120545</v>
       </c>
       <c r="C15">
-        <v>32.851</v>
+        <v>28.386</v>
       </c>
       <c r="D15">
-        <v>31.829</v>
+        <v>27.586</v>
       </c>
       <c r="E15">
-        <v>33.898</v>
+        <v>29.162</v>
       </c>
     </row>
     <row r="16">
@@ -1070,16 +1070,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>31.34510361512118</v>
+        <v>26.91418648523269</v>
       </c>
       <c r="C16">
-        <v>31.345</v>
+        <v>26.914</v>
       </c>
       <c r="D16">
-        <v>30.288</v>
+        <v>26.132</v>
       </c>
       <c r="E16">
-        <v>32.358</v>
+        <v>27.687</v>
       </c>
     </row>
     <row r="17">
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>29.99260749910851</v>
+        <v>25.92579763307756</v>
       </c>
       <c r="C17">
-        <v>29.993</v>
+        <v>25.926</v>
       </c>
       <c r="D17">
-        <v>28.934</v>
+        <v>25.182</v>
       </c>
       <c r="E17">
-        <v>31.015</v>
+        <v>26.705</v>
       </c>
     </row>
     <row r="18">
@@ -1104,16 +1104,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28.26546445251643</v>
+        <v>24.63002700746719</v>
       </c>
       <c r="C18">
-        <v>28.265</v>
+        <v>24.63</v>
       </c>
       <c r="D18">
-        <v>27.355</v>
+        <v>23.926</v>
       </c>
       <c r="E18">
-        <v>29.186</v>
+        <v>25.352</v>
       </c>
     </row>
     <row r="19">
@@ -1121,16 +1121,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>27.86072196154047</v>
+        <v>24.10181441383856</v>
       </c>
       <c r="C19">
-        <v>27.861</v>
+        <v>24.102</v>
       </c>
       <c r="D19">
-        <v>26.943</v>
+        <v>23.408</v>
       </c>
       <c r="E19">
-        <v>28.818</v>
+        <v>24.806</v>
       </c>
     </row>
     <row r="20">
@@ -1138,16 +1138,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.38066606134837</v>
+        <v>23.77989822653389</v>
       </c>
       <c r="C20">
-        <v>27.381</v>
+        <v>23.78</v>
       </c>
       <c r="D20">
-        <v>26.418</v>
+        <v>23.069</v>
       </c>
       <c r="E20">
-        <v>28.382</v>
+        <v>24.523</v>
       </c>
     </row>
     <row r="21">
@@ -1155,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25.43697462656533</v>
+        <v>22.08666171881933</v>
       </c>
       <c r="C21">
-        <v>25.437</v>
+        <v>22.087</v>
       </c>
       <c r="D21">
-        <v>24.529</v>
+        <v>21.401</v>
       </c>
       <c r="E21">
-        <v>26.365</v>
+        <v>22.798</v>
       </c>
     </row>
     <row r="22">
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>26.22347496520407</v>
+        <v>22.630028498106</v>
       </c>
       <c r="C22">
-        <v>26.223</v>
+        <v>22.63</v>
       </c>
       <c r="D22">
-        <v>25.251</v>
+        <v>21.889</v>
       </c>
       <c r="E22">
-        <v>27.206</v>
+        <v>23.348</v>
       </c>
     </row>
     <row r="23">
@@ -1189,16 +1189,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>23.57760119763544</v>
+        <v>20.50322960484755</v>
       </c>
       <c r="C23">
-        <v>23.578</v>
+        <v>20.503</v>
       </c>
       <c r="D23">
-        <v>22.652</v>
+        <v>19.838</v>
       </c>
       <c r="E23">
-        <v>24.456</v>
+        <v>21.168</v>
       </c>
     </row>
     <row r="24">
@@ -1206,16 +1206,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>24.27030491360938</v>
+        <v>20.98336103074752</v>
       </c>
       <c r="C24">
-        <v>24.27</v>
+        <v>20.983</v>
       </c>
       <c r="D24">
-        <v>23.354</v>
+        <v>20.266</v>
       </c>
       <c r="E24">
-        <v>25.213</v>
+        <v>21.702</v>
       </c>
     </row>
     <row r="25">
@@ -1223,16 +1223,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>22.81856252000242</v>
+        <v>19.03795910418179</v>
       </c>
       <c r="C25">
-        <v>22.819</v>
+        <v>19.038</v>
       </c>
       <c r="D25">
-        <v>21.898</v>
+        <v>18.401</v>
       </c>
       <c r="E25">
-        <v>23.737</v>
+        <v>19.675</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/Output_monthly_mean_costs-Unadjusted.xlsx
+++ b/Comparison Analysis/Results/Output_monthly_mean_costs-Unadjusted.xlsx
@@ -387,16 +387,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>99.05867804288665</v>
+        <v>349.5601982813883</v>
       </c>
       <c r="C2">
-        <v>99.059</v>
+        <v>349.56</v>
       </c>
       <c r="D2">
-        <v>97.711</v>
+        <v>343.242</v>
       </c>
       <c r="E2">
-        <v>100.429</v>
+        <v>355.86</v>
       </c>
     </row>
     <row r="3">
@@ -404,16 +404,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>69.80736881636767</v>
+        <v>250.459762603148</v>
       </c>
       <c r="C3">
-        <v>69.807</v>
+        <v>250.46</v>
       </c>
       <c r="D3">
-        <v>68.63</v>
+        <v>244.894</v>
       </c>
       <c r="E3">
-        <v>70.986</v>
+        <v>256.103</v>
       </c>
     </row>
     <row r="4">
@@ -421,16 +421,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>63.95476160804262</v>
+        <v>240.0941980033692</v>
       </c>
       <c r="C4">
-        <v>63.955</v>
+        <v>240.094</v>
       </c>
       <c r="D4">
-        <v>62.781</v>
+        <v>234.232</v>
       </c>
       <c r="E4">
-        <v>65.087</v>
+        <v>246.06</v>
       </c>
     </row>
     <row r="5">
@@ -438,16 +438,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>53.12185586057736</v>
+        <v>201.1375232351182</v>
       </c>
       <c r="C5">
-        <v>53.122</v>
+        <v>201.138</v>
       </c>
       <c r="D5">
-        <v>52.063</v>
+        <v>195.852</v>
       </c>
       <c r="E5">
-        <v>54.182</v>
+        <v>206.389</v>
       </c>
     </row>
     <row r="6">
@@ -455,16 +455,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>48.50953159837668</v>
+        <v>186.6667329657832</v>
       </c>
       <c r="C6">
-        <v>48.51</v>
+        <v>186.667</v>
       </c>
       <c r="D6">
-        <v>47.483</v>
+        <v>181.08</v>
       </c>
       <c r="E6">
-        <v>49.526</v>
+        <v>192.399</v>
       </c>
     </row>
     <row r="7">
@@ -472,16 +472,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>43.3334185263894</v>
+        <v>164.3715295040174</v>
       </c>
       <c r="C7">
-        <v>43.333</v>
+        <v>164.372</v>
       </c>
       <c r="D7">
-        <v>42.414</v>
+        <v>159.467</v>
       </c>
       <c r="E7">
-        <v>44.306</v>
+        <v>169.541</v>
       </c>
     </row>
     <row r="8">
@@ -489,16 +489,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>41.56185486553372</v>
+        <v>159.4112496133552</v>
       </c>
       <c r="C8">
-        <v>41.562</v>
+        <v>159.411</v>
       </c>
       <c r="D8">
-        <v>40.606</v>
+        <v>154.43</v>
       </c>
       <c r="E8">
-        <v>42.529</v>
+        <v>164.25</v>
       </c>
     </row>
     <row r="9">
@@ -506,16 +506,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>37.7925320473974</v>
+        <v>148.7394531467673</v>
       </c>
       <c r="C9">
-        <v>37.793</v>
+        <v>148.739</v>
       </c>
       <c r="D9">
-        <v>36.884</v>
+        <v>143.87</v>
       </c>
       <c r="E9">
-        <v>38.667</v>
+        <v>153.644</v>
       </c>
     </row>
     <row r="10">
@@ -523,16 +523,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>37.1954066722423</v>
+        <v>144.9290699714977</v>
       </c>
       <c r="C10">
-        <v>37.195</v>
+        <v>144.929</v>
       </c>
       <c r="D10">
-        <v>36.282</v>
+        <v>139.99</v>
       </c>
       <c r="E10">
-        <v>38.114</v>
+        <v>149.884</v>
       </c>
     </row>
     <row r="11">
@@ -540,16 +540,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>35.62409598657737</v>
+        <v>140.0160839915163</v>
       </c>
       <c r="C11">
-        <v>35.624</v>
+        <v>140.016</v>
       </c>
       <c r="D11">
-        <v>34.695</v>
+        <v>134.877</v>
       </c>
       <c r="E11">
-        <v>36.552</v>
+        <v>145.177</v>
       </c>
     </row>
     <row r="12">
@@ -557,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>33.40428925160928</v>
+        <v>132.3980370624534</v>
       </c>
       <c r="C12">
-        <v>33.404</v>
+        <v>132.398</v>
       </c>
       <c r="D12">
-        <v>32.574</v>
+        <v>127.798</v>
       </c>
       <c r="E12">
-        <v>34.228</v>
+        <v>137.014</v>
       </c>
     </row>
     <row r="13">
@@ -574,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>34.21152591672208</v>
+        <v>134.24535880837</v>
       </c>
       <c r="C13">
-        <v>34.212</v>
+        <v>134.245</v>
       </c>
       <c r="D13">
-        <v>33.304</v>
+        <v>129.309</v>
       </c>
       <c r="E13">
-        <v>35.11</v>
+        <v>139.119</v>
       </c>
     </row>
     <row r="14">
@@ -591,16 +591,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>31.57264273751825</v>
+        <v>124.8105872071384</v>
       </c>
       <c r="C14">
-        <v>31.573</v>
+        <v>124.811</v>
       </c>
       <c r="D14">
-        <v>30.747</v>
+        <v>120.4</v>
       </c>
       <c r="E14">
-        <v>32.363</v>
+        <v>129.233</v>
       </c>
     </row>
     <row r="15">
@@ -608,16 +608,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>31.11714387652273</v>
+        <v>122.1528524042311</v>
       </c>
       <c r="C15">
-        <v>31.117</v>
+        <v>122.153</v>
       </c>
       <c r="D15">
-        <v>30.259</v>
+        <v>117.598</v>
       </c>
       <c r="E15">
-        <v>31.973</v>
+        <v>126.819</v>
       </c>
     </row>
     <row r="16">
@@ -625,16 +625,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>29.43357940845804</v>
+        <v>114.7686446588807</v>
       </c>
       <c r="C16">
-        <v>29.434</v>
+        <v>114.769</v>
       </c>
       <c r="D16">
-        <v>28.617</v>
+        <v>110.327</v>
       </c>
       <c r="E16">
-        <v>30.227</v>
+        <v>119.105</v>
       </c>
     </row>
     <row r="17">
@@ -642,16 +642,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28.57380668938049</v>
+        <v>112.0674088738405</v>
       </c>
       <c r="C17">
-        <v>28.574</v>
+        <v>112.067</v>
       </c>
       <c r="D17">
-        <v>27.729</v>
+        <v>107.605</v>
       </c>
       <c r="E17">
-        <v>29.426</v>
+        <v>116.579</v>
       </c>
     </row>
     <row r="18">
@@ -659,16 +659,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>27.05234608666443</v>
+        <v>108.1776890863125</v>
       </c>
       <c r="C18">
-        <v>27.052</v>
+        <v>108.178</v>
       </c>
       <c r="D18">
-        <v>26.263</v>
+        <v>103.791</v>
       </c>
       <c r="E18">
-        <v>27.834</v>
+        <v>112.303</v>
       </c>
     </row>
     <row r="19">
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>26.55599132738752</v>
+        <v>105.5106595062864</v>
       </c>
       <c r="C19">
-        <v>26.556</v>
+        <v>105.511</v>
       </c>
       <c r="D19">
-        <v>25.748</v>
+        <v>101.264</v>
       </c>
       <c r="E19">
-        <v>27.37</v>
+        <v>109.843</v>
       </c>
     </row>
     <row r="20">
@@ -693,16 +693,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>26.15764604519</v>
+        <v>103.2753137043055</v>
       </c>
       <c r="C20">
-        <v>26.158</v>
+        <v>103.275</v>
       </c>
       <c r="D20">
-        <v>25.387</v>
+        <v>99.07599999999999</v>
       </c>
       <c r="E20">
-        <v>26.924</v>
+        <v>107.347</v>
       </c>
     </row>
     <row r="21">
@@ -710,16 +710,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>24.28707693575919</v>
+        <v>96.22461442176346</v>
       </c>
       <c r="C21">
-        <v>24.287</v>
+        <v>96.22499999999999</v>
       </c>
       <c r="D21">
-        <v>23.508</v>
+        <v>92.077</v>
       </c>
       <c r="E21">
-        <v>25.028</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="22">
@@ -727,16 +727,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>24.89110474111042</v>
+        <v>98.538577971805</v>
       </c>
       <c r="C22">
-        <v>24.891</v>
+        <v>98.539</v>
       </c>
       <c r="D22">
-        <v>24.093</v>
+        <v>94.25700000000001</v>
       </c>
       <c r="E22">
-        <v>25.655</v>
+        <v>102.602</v>
       </c>
     </row>
     <row r="23">
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>22.61530467358593</v>
+        <v>91.78133362884248</v>
       </c>
       <c r="C23">
-        <v>22.615</v>
+        <v>91.78100000000001</v>
       </c>
       <c r="D23">
-        <v>21.902</v>
+        <v>87.774</v>
       </c>
       <c r="E23">
-        <v>23.339</v>
+        <v>95.801</v>
       </c>
     </row>
     <row r="24">
@@ -761,16 +761,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>22.94278394151077</v>
+        <v>91.32954056938745</v>
       </c>
       <c r="C24">
-        <v>22.943</v>
+        <v>91.33</v>
       </c>
       <c r="D24">
-        <v>22.18</v>
+        <v>87.532</v>
       </c>
       <c r="E24">
-        <v>23.722</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="25">
@@ -778,16 +778,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>20.85801345999603</v>
+        <v>83.68060257514183</v>
       </c>
       <c r="C25">
-        <v>20.858</v>
+        <v>83.681</v>
       </c>
       <c r="D25">
-        <v>20.119</v>
+        <v>79.60299999999999</v>
       </c>
       <c r="E25">
-        <v>21.586</v>
+        <v>87.59</v>
       </c>
     </row>
   </sheetData>
@@ -832,16 +832,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>90.82146312041387</v>
+        <v>114.2845075409815</v>
       </c>
       <c r="C2">
-        <v>90.821</v>
+        <v>114.285</v>
       </c>
       <c r="D2">
-        <v>89.62</v>
+        <v>112.518</v>
       </c>
       <c r="E2">
-        <v>92.063</v>
+        <v>116.097</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>63.81400316927204</v>
+        <v>80.9846820303536</v>
       </c>
       <c r="C3">
-        <v>63.814</v>
+        <v>80.985</v>
       </c>
       <c r="D3">
-        <v>62.733</v>
+        <v>79.425</v>
       </c>
       <c r="E3">
-        <v>64.883</v>
+        <v>82.53</v>
       </c>
     </row>
     <row r="4">
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>58.46920665064061</v>
+        <v>74.79965774756812</v>
       </c>
       <c r="C4">
-        <v>58.469</v>
+        <v>74.8</v>
       </c>
       <c r="D4">
-        <v>57.413</v>
+        <v>73.28400000000001</v>
       </c>
       <c r="E4">
-        <v>59.539</v>
+        <v>76.32599999999999</v>
       </c>
     </row>
     <row r="5">
@@ -883,16 +883,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>48.36305309052091</v>
+        <v>61.77670443375931</v>
       </c>
       <c r="C5">
-        <v>48.363</v>
+        <v>61.777</v>
       </c>
       <c r="D5">
-        <v>47.443</v>
+        <v>60.461</v>
       </c>
       <c r="E5">
-        <v>49.295</v>
+        <v>63.103</v>
       </c>
     </row>
     <row r="6">
@@ -900,16 +900,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>44.05150886515644</v>
+        <v>56.49247053548225</v>
       </c>
       <c r="C6">
-        <v>44.052</v>
+        <v>56.492</v>
       </c>
       <c r="D6">
-        <v>43.11</v>
+        <v>55.137</v>
       </c>
       <c r="E6">
-        <v>44.989</v>
+        <v>57.841</v>
       </c>
     </row>
     <row r="7">
@@ -917,16 +917,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>39.37389950431164</v>
+        <v>50.52080001846248</v>
       </c>
       <c r="C7">
-        <v>39.374</v>
+        <v>50.521</v>
       </c>
       <c r="D7">
-        <v>38.518</v>
+        <v>49.278</v>
       </c>
       <c r="E7">
-        <v>40.252</v>
+        <v>51.785</v>
       </c>
     </row>
     <row r="8">
@@ -934,16 +934,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>37.81484531259321</v>
+        <v>48.75955357477429</v>
       </c>
       <c r="C8">
-        <v>37.815</v>
+        <v>48.76</v>
       </c>
       <c r="D8">
-        <v>36.923</v>
+        <v>47.515</v>
       </c>
       <c r="E8">
-        <v>38.682</v>
+        <v>49.993</v>
       </c>
     </row>
     <row r="9">
@@ -951,16 +951,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>34.28728516389078</v>
+        <v>44.38335426906753</v>
       </c>
       <c r="C9">
-        <v>34.287</v>
+        <v>44.383</v>
       </c>
       <c r="D9">
-        <v>33.431</v>
+        <v>43.124</v>
       </c>
       <c r="E9">
-        <v>35.142</v>
+        <v>45.618</v>
       </c>
     </row>
     <row r="10">
@@ -968,16 +968,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>33.91752810234615</v>
+        <v>43.58566748897125</v>
       </c>
       <c r="C10">
-        <v>33.918</v>
+        <v>43.586</v>
       </c>
       <c r="D10">
-        <v>33.091</v>
+        <v>42.414</v>
       </c>
       <c r="E10">
-        <v>34.763</v>
+        <v>44.788</v>
       </c>
     </row>
     <row r="11">
@@ -985,16 +985,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>32.5645593321123</v>
+        <v>42.1541583056901</v>
       </c>
       <c r="C11">
-        <v>32.565</v>
+        <v>42.154</v>
       </c>
       <c r="D11">
-        <v>31.709</v>
+        <v>40.963</v>
       </c>
       <c r="E11">
-        <v>33.39</v>
+        <v>43.298</v>
       </c>
     </row>
     <row r="12">
@@ -1002,16 +1002,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>30.44006724826039</v>
+        <v>39.07157023173762</v>
       </c>
       <c r="C12">
-        <v>30.44</v>
+        <v>39.072</v>
       </c>
       <c r="D12">
-        <v>29.604</v>
+        <v>37.92</v>
       </c>
       <c r="E12">
-        <v>31.228</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="13">
@@ -1019,16 +1019,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>31.27010472960533</v>
+        <v>40.44977720525499</v>
       </c>
       <c r="C13">
-        <v>31.27</v>
+        <v>40.45</v>
       </c>
       <c r="D13">
-        <v>30.423</v>
+        <v>39.245</v>
       </c>
       <c r="E13">
-        <v>32.146</v>
+        <v>41.704</v>
       </c>
     </row>
     <row r="14">
@@ -1036,16 +1036,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>28.73185078501769</v>
+        <v>36.93807778170692</v>
       </c>
       <c r="C14">
-        <v>28.732</v>
+        <v>36.938</v>
       </c>
       <c r="D14">
-        <v>27.979</v>
+        <v>35.88</v>
       </c>
       <c r="E14">
-        <v>29.512</v>
+        <v>38.044</v>
       </c>
     </row>
     <row r="15">
@@ -1053,16 +1053,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>28.3857398120545</v>
+        <v>36.66178480316603</v>
       </c>
       <c r="C15">
-        <v>28.386</v>
+        <v>36.662</v>
       </c>
       <c r="D15">
-        <v>27.586</v>
+        <v>35.527</v>
       </c>
       <c r="E15">
-        <v>29.162</v>
+        <v>37.774</v>
       </c>
     </row>
     <row r="16">
@@ -1070,16 +1070,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.91418648523269</v>
+        <v>34.8333260921529</v>
       </c>
       <c r="C16">
-        <v>26.914</v>
+        <v>34.833</v>
       </c>
       <c r="D16">
-        <v>26.132</v>
+        <v>33.716</v>
       </c>
       <c r="E16">
-        <v>27.687</v>
+        <v>35.934</v>
       </c>
     </row>
     <row r="17">
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25.92579763307756</v>
+        <v>33.5070763129869</v>
       </c>
       <c r="C17">
-        <v>25.926</v>
+        <v>33.507</v>
       </c>
       <c r="D17">
-        <v>25.182</v>
+        <v>32.464</v>
       </c>
       <c r="E17">
-        <v>26.705</v>
+        <v>34.599</v>
       </c>
     </row>
     <row r="18">
@@ -1104,16 +1104,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>24.63002700746719</v>
+        <v>31.99669123945491</v>
       </c>
       <c r="C18">
-        <v>24.63</v>
+        <v>31.997</v>
       </c>
       <c r="D18">
-        <v>23.926</v>
+        <v>30.995</v>
       </c>
       <c r="E18">
-        <v>25.352</v>
+        <v>33.031</v>
       </c>
     </row>
     <row r="19">
@@ -1121,16 +1121,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>24.10181441383856</v>
+        <v>31.13850684628169</v>
       </c>
       <c r="C19">
-        <v>24.102</v>
+        <v>31.139</v>
       </c>
       <c r="D19">
-        <v>23.408</v>
+        <v>30.164</v>
       </c>
       <c r="E19">
-        <v>24.806</v>
+        <v>32.127</v>
       </c>
     </row>
     <row r="20">
@@ -1138,16 +1138,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>23.77989822653389</v>
+        <v>31.03718115826321</v>
       </c>
       <c r="C20">
-        <v>23.78</v>
+        <v>31.037</v>
       </c>
       <c r="D20">
-        <v>23.069</v>
+        <v>29.994</v>
       </c>
       <c r="E20">
-        <v>24.523</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="21">
@@ -1155,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22.08666171881933</v>
+        <v>28.69973548225997</v>
       </c>
       <c r="C21">
-        <v>22.087</v>
+        <v>28.7</v>
       </c>
       <c r="D21">
-        <v>21.401</v>
+        <v>27.722</v>
       </c>
       <c r="E21">
-        <v>22.798</v>
+        <v>29.718</v>
       </c>
     </row>
     <row r="22">
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>22.630028498106</v>
+        <v>29.49174646138439</v>
       </c>
       <c r="C22">
-        <v>22.63</v>
+        <v>29.492</v>
       </c>
       <c r="D22">
-        <v>21.889</v>
+        <v>28.43</v>
       </c>
       <c r="E22">
-        <v>23.348</v>
+        <v>30.509</v>
       </c>
     </row>
     <row r="23">
@@ -1189,16 +1189,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>20.50322960484755</v>
+        <v>26.86323740890713</v>
       </c>
       <c r="C23">
-        <v>20.503</v>
+        <v>26.863</v>
       </c>
       <c r="D23">
-        <v>19.838</v>
+        <v>25.901</v>
       </c>
       <c r="E23">
-        <v>21.168</v>
+        <v>27.813</v>
       </c>
     </row>
     <row r="24">
@@ -1206,16 +1206,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>20.98336103074752</v>
+        <v>27.12204353470276</v>
       </c>
       <c r="C24">
-        <v>20.983</v>
+        <v>27.122</v>
       </c>
       <c r="D24">
-        <v>20.266</v>
+        <v>26.117</v>
       </c>
       <c r="E24">
-        <v>21.702</v>
+        <v>28.131</v>
       </c>
     </row>
     <row r="25">
@@ -1223,16 +1223,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>19.03795910418179</v>
+        <v>25.02610690462387</v>
       </c>
       <c r="C25">
-        <v>19.038</v>
+        <v>25.026</v>
       </c>
       <c r="D25">
-        <v>18.401</v>
+        <v>24.114</v>
       </c>
       <c r="E25">
-        <v>19.675</v>
+        <v>25.945</v>
       </c>
     </row>
   </sheetData>
